--- a/data/anova--carrier_delivery.xlsx
+++ b/data/anova--carrier_delivery.xlsx
@@ -5415,7 +5415,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: completed shipments across THREE carriers.</t>
+          <t>WHAT IS CAPTURED: completed shipments across THREE carriers (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
